--- a/10_企画書・プロジェクト企画書/10_企画書.xlsx
+++ b/10_企画書・プロジェクト企画書/10_企画書.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E4DD7E-9389-4B60-86D8-23904A8F0B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BE7C69-AF24-4F4E-992F-95FA2D3AD0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>企画書</t>
     <rPh sb="0" eb="3">
@@ -168,38 +168,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4．罹災証明書の申請案内機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被災者が罹災証明書を申請する際に必要となる手続きや申請方法、必要書類などの情報を案内する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>5．修理業者の情報提示機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況や修理内容に応じて、利用可能な修理業者の情報を提示し、業者探しを支援する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>6．被災後の対応案内機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被害状況に応じて、修理や各種申請など、被災後に必要となる対応を順番に案内することで、</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被災者が次に何をすべきかを分かりやすくする。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>7．被害状況・分析履歴機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>過去に登録した被害状況の写真やAIによる分析結果を履歴として保存し、後から確認できる機能。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -209,44 +177,6 @@
   </si>
   <si>
     <t>利用者が回答することで、画像だけでは判断できない情報も収集する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>提案先：建物調査を実施している企業、修理業者</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>キギョウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>シュウリ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ギョウシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>手間と費用がかかり、また悪徳業者に不当な契約をされるリスクがある。</t>
-    <rPh sb="12" eb="14">
-      <t>アクトク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ギョウシャ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>フトウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ケイヤク</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -257,40 +187,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>利用者：災害によって建物や室内に被害を受けた個人・事業者・建物管理者</t>
-    <rPh sb="0" eb="3">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サイガイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シツナイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>ジギョウシャ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="31" eb="34">
-      <t>カンリシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>行政向けには建物内部の被害状況を確認する類似システムが存在するが、</t>
     <rPh sb="0" eb="2">
       <t>ギョウセイ</t>
@@ -337,6 +233,127 @@
   </si>
   <si>
     <t>tanouesoftware</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者：災害によって建物や室内に被害を受けた個人</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイガイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シツナイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>コジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5．被害状況・分析履歴機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提案先：被災後の復旧対応を行う自治体・修理業者</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒサイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フッキュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジチタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウリ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ギョウシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>手間と費用がかかり、また悪徳業者に不当な契約をされるリスクもある。</t>
+    <rPh sb="12" eb="14">
+      <t>アクトク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ギョウシャ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>フトウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケイヤク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．各種申請書・支援制度の案内機能</t>
+    <rPh sb="2" eb="4">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>シンセイショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者が申請書・支援制度を申請する際に必要となる手続きや申請方法、必要書類などの</t>
+    <rPh sb="4" eb="7">
+      <t>シンセイショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シエン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報を案内し、被災者と自治体の橋渡しの役割を担う。</t>
+    <rPh sb="7" eb="10">
+      <t>ヒサイシャ</t>
+    </rPh>
+    <rPh sb="11" eb="14">
+      <t>ジチタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ハシワタ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -592,6 +609,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -601,7 +621,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -617,39 +667,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2798,7 +2815,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2809,9 +2826,9 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="11" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C3" s="10">
         <v>46283</v>
@@ -2821,18 +2838,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="26"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -2845,43 +2862,43 @@
       <c r="A8" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
     </row>
     <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="14"/>
+      <c r="A11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="14"/>
+      <c r="A12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
     </row>
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="17"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2894,134 +2911,126 @@
       <c r="A15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="22"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="15"/>
     </row>
     <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="16"/>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="16"/>
+    </row>
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12"/>
+      <c r="C22" s="16"/>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="16"/>
+    </row>
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="16"/>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+    </row>
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="16"/>
+    </row>
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="16"/>
+    </row>
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
-    </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25"/>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" s="24"/>
-      <c r="C23" s="25"/>
-    </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="24" t="s">
+      <c r="B28" s="12"/>
+      <c r="C28" s="16"/>
+    </row>
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-    </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
-    </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="25"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="25"/>
-    </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="24"/>
-      <c r="C29" s="25"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="16"/>
     </row>
     <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="25"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="16"/>
     </row>
     <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="16"/>
     </row>
     <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="16"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
@@ -3031,28 +3040,28 @@
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
+      <c r="A35" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23"/>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="A36" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="12"/>
+      <c r="C36" s="16"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="12"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="25"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="16"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="15"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="28"/>
+      <c r="A38" s="18"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
     </row>
     <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
@@ -3063,37 +3072,58 @@
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30"/>
+        <v>25</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="23"/>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="25"/>
+      <c r="A41" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="16"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="14"/>
+      <c r="A42" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="15"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="12"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
+      <c r="A44" s="13"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A44:C44"/>
@@ -3110,27 +3140,6 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3142,6 +3151,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3348,27 +3377,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3385,25 +3415,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/10_企画書・プロジェクト企画書/10_企画書.xlsx
+++ b/10_企画書・プロジェクト企画書/10_企画書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k_tanoue\Documents\GitHub\tanouesoftware\10_企画書・プロジェクト企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BE7C69-AF24-4F4E-992F-95FA2D3AD0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D748AA01-CBE8-4BAE-AE3F-B8C50999F06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -116,10 +116,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>地震で被災した建造物の被害状況を文字や画像で送信し、工事が必要か診断する</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>先日発生した令和8年熊本地震により多くの家屋が被害を受けた。</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -228,74 +224,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>こうした背景から、利用者自身が自宅内部の状況を確認できるシステムが必要だと考えた。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>tanouesoftware</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>利用者：災害によって建物や室内に被害を受けた個人</t>
-    <rPh sb="0" eb="3">
-      <t>リヨウシャ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サイガイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>タテモノ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>シツナイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヒガイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ウ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>コジン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>5．被害状況・分析履歴機能</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>提案先：被災後の復旧対応を行う自治体・修理業者</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>サキ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒサイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>フッキュウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>タイオウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>ジチタイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>シュウリ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ギョウシャ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -315,44 +244,112 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>提案先：被災後の復旧対応を行う自治体</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒサイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>フッキュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>ジチタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>利用者：災害によって建物に被害を受けた個人</t>
+    <rPh sb="0" eb="3">
+      <t>リヨウシャ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイガイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>コジン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こうした背景から、利用者自身が建物内部の被害状況の目安を確認できるシステムが必要だと考えた。</t>
+    <rPh sb="15" eb="17">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>メヤス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>情報を案内し、被災者と自治体の橋渡しの役割を担う。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>被災者が申請書・支援制度を申請する際に必要となる手続きや申請方法、必要書類などの</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>4．各種申請書・支援制度の案内機能</t>
-    <rPh sb="2" eb="4">
-      <t>カクシュ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>シンセイショ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シエン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>セイド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>被災者が申請書・支援制度を申請する際に必要となる手続きや申請方法、必要書類などの</t>
-    <rPh sb="4" eb="7">
-      <t>シンセイショ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シエン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>セイド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>情報を案内し、被災者と自治体の橋渡しの役割を担う。</t>
-    <rPh sb="7" eb="10">
-      <t>ヒサイシャ</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ジチタイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ハシワタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>チーム田上</t>
+    <rPh sb="3" eb="5">
+      <t>タノウエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地震で被災した建物の被害状況をAIで分析し、被害の目安や今後の対応を示す</t>
+    <rPh sb="7" eb="9">
+      <t>タテモノ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヒガイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>メヤス</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>コンゴ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>シメ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -572,7 +569,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -609,9 +606,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -621,37 +615,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -667,6 +631,42 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2815,7 +2815,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -2826,9 +2826,9 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="29"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C3" s="10">
         <v>46283</v>
@@ -2838,18 +2838,18 @@
       <c r="B4" s="1"/>
     </row>
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="26"/>
+        <v>35</v>
+      </c>
+      <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="17"/>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
@@ -2860,45 +2860,45 @@
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="23"/>
+      <c r="C8" s="22"/>
+    </row>
+    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="13"/>
+      <c r="C9" s="14"/>
+    </row>
+    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-    </row>
-    <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
+    </row>
+    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14"/>
+    </row>
+    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="14"/>
+    </row>
+    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15"/>
-    </row>
-    <row r="10" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
-    </row>
-    <row r="11" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-    </row>
-    <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-    </row>
-    <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="28"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="17"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -2909,128 +2909,128 @@
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="22"/>
+    </row>
+    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-    </row>
-    <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+    </row>
+    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+    </row>
+    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-    </row>
-    <row r="17" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15"/>
-    </row>
-    <row r="18" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-    </row>
-    <row r="19" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="25"/>
+    </row>
+    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="25"/>
+    </row>
+    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="16"/>
-    </row>
-    <row r="21" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="16"/>
-    </row>
-    <row r="22" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+    </row>
+    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="25"/>
+    </row>
+    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+    </row>
+    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="B26" s="24"/>
+      <c r="C26" s="25"/>
+    </row>
+    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="12"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
+    </row>
+    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="25"/>
+    </row>
+    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
+    </row>
+    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="32"/>
+      <c r="C30" s="14"/>
+    </row>
+    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="12"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
+    </row>
+    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
+    </row>
+    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="16"/>
-    </row>
-    <row r="25" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-    </row>
-    <row r="26" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="16"/>
-    </row>
-    <row r="27" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="16"/>
-    </row>
-    <row r="28" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="16"/>
-    </row>
-    <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="16"/>
-    </row>
-    <row r="30" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="16"/>
-    </row>
-    <row r="31" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="16"/>
-    </row>
-    <row r="32" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="16"/>
-    </row>
-    <row r="33" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="16"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="17"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
@@ -3040,28 +3040,28 @@
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
+      <c r="A35" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30"/>
     </row>
     <row r="36" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="12"/>
-      <c r="C36" s="16"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
     </row>
     <row r="37" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="16"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="20"/>
+      <c r="A38" s="15"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="28"/>
     </row>
     <row r="39" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
@@ -3072,58 +3072,37 @@
     </row>
     <row r="40" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30"/>
+    </row>
+    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
-    </row>
-    <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="16"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="25"/>
     </row>
     <row r="42" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="15"/>
+      <c r="A42" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="14"/>
     </row>
     <row r="43" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
     </row>
     <row r="44" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="16"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A44:C44"/>
@@ -3140,6 +3119,27 @@
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -3151,26 +3151,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x01010058BEBA3CD4E69545839402B5D4E5400B" ma:contentTypeVersion="13" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="85fadafb228503a8e253560e9cdffc69">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88cc3c26-756f-41ab-80ed-43e7289fee5b" xmlns:ns3="55239288-d498-4dd6-9609-491b39ec8fae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9785dde68d2e35ac7b66dd15e8e44124" ns2:_="" ns3:_="">
     <xsd:import namespace="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
@@ -3377,28 +3357,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
-    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
-    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
-    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88cc3c26-756f-41ab-80ed-43e7289fee5b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="55239288-d498-4dd6-9609-491b39ec8fae" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0418D70-73DB-44BD-BD7C-28097BDA85A0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3415,4 +3394,25 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5563C4DF-5E30-4883-BC53-5FA5B697DAFD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CD14F3A-D824-479D-BAC6-CDB85BCAF907}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="96e9746f-acab-410f-8363-815e1ac6f97e"/>
+    <ds:schemaRef ds:uri="4707ffff-3746-4042-a13f-bfbbbbe730e0"/>
+    <ds:schemaRef ds:uri="88cc3c26-756f-41ab-80ed-43e7289fee5b"/>
+    <ds:schemaRef ds:uri="55239288-d498-4dd6-9609-491b39ec8fae"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>